--- a/data/fmsForecastOutput/File1/RPT_RPT3930929415984ET_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3930929415984ET_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,22 +1875,22 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>360.8432324213941</v>
+        <v>360.8432324213942</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>397.5823581854566</v>
+        <v>397.5823581854565</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>436.0703541058002</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>467.6283578056763</v>
+        <v>467.6283578056762</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>505.2193161238809</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>37.95734072766477</v>
+        <v>37.95734072766478</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>43.6672240408253</v>
@@ -1899,16 +1899,16 @@
         <v>50.05983533348703</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>56.6164128588219</v>
+        <v>56.61641285882189</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>64.93285954696169</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>46968978.51875804</v>
+        <v>46968978.51875805</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>54905364.79002439</v>
+        <v>54905364.7900244</v>
       </c>
       <c r="O8" s="152" t="n">
         <v>63853119.24475222</v>
@@ -1925,22 +1925,22 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>437.6338895104269</v>
+        <v>437.633889510427</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>482.1914287981892</v>
+        <v>482.1914287981891</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>528.8700134041806</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>567.1438416583095</v>
+        <v>567.1438416583094</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>612.7344910625599</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.98162310228414</v>
+        <v>46.98162310228415</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>54.04325572399413</v>
@@ -1955,10 +1955,10 @@
         <v>80.32744540643422</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>46968978.51875804</v>
+        <v>46968978.51875805</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>54905364.79002439</v>
+        <v>54905364.7900244</v>
       </c>
       <c r="AF8" s="152" t="n">
         <v>63853119.24475222</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>843.8768162922768</v>
+        <v>843.8768162922764</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>936.5563090164418</v>
@@ -2037,19 +2037,19 @@
         <v>1146.529052835005</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>59.36287213537634</v>
+        <v>59.36287213537632</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>66.88229688076962</v>
+        <v>66.88229688076963</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>76.03645831900904</v>
+        <v>76.03645831900907</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>85.216615243419</v>
+        <v>85.21661524341899</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>96.89026167873936</v>
+        <v>96.89026167873935</v>
       </c>
       <c r="M9" s="158" t="n">
         <v>16051068.42212362</v>
@@ -2064,7 +2064,7 @@
         <v>23510955.76210605</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>26957478.10373134</v>
+        <v>26957478.10373133</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>855.9568829780013</v>
+        <v>855.956882978001</v>
       </c>
       <c r="U9" s="156" t="n">
         <v>949.9630793523816</v>
@@ -2081,25 +2081,25 @@
         <v>1041.521873172326</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1097.771362360756</v>
+        <v>1097.771362360755</v>
       </c>
       <c r="X9" s="157" t="n">
         <v>1162.941575549185</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>59.61199779480659</v>
+        <v>59.61199779480658</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>67.1637483848064</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>76.35859284658243</v>
+        <v>76.35859284658244</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>85.58194745210342</v>
+        <v>85.58194745210341</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>97.31166476774378</v>
+        <v>97.31166476774376</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>16051068.42212362</v>
@@ -2114,7 +2114,7 @@
         <v>23510955.76210605</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>26957478.10373134</v>
+        <v>26957478.10373133</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2176,37 +2176,37 @@
         <v>464.1200286038674</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>508.0179470973346</v>
+        <v>508.0179470973347</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>542.5500924626085</v>
+        <v>542.5500924626084</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>583.5961039947749</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>41.79591715779956</v>
+        <v>41.79591715779957</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>47.80050320800936</v>
+        <v>47.80050320800937</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>54.65634921982129</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>61.64721565606548</v>
+        <v>61.64721565606547</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>70.51729521147681</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>63020046.94088166</v>
+        <v>63020046.94088167</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>73121067.08068204</v>
+        <v>73121067.08068205</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>84704424.20462848</v>
+        <v>84704424.2046285</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>96692164.63041431</v>
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>499.853585281896</v>
+        <v>499.8535852818961</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>549.6110000772015</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>601.7861167785708</v>
+        <v>601.7861167785709</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>642.6793627215295</v>
+        <v>642.6793627215294</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>691.2582163051452</v>
@@ -2238,10 +2238,10 @@
         <v>49.66158329373054</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>56.80782031906527</v>
+        <v>56.80782031906528</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>64.96595308458602</v>
+        <v>64.96595308458603</v>
       </c>
       <c r="AB10" s="162" t="n">
         <v>73.28500352936922</v>
@@ -2250,13 +2250,13 @@
         <v>83.84085424871321</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>63020046.94088166</v>
+        <v>63020046.94088167</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>73121067.08068204</v>
+        <v>73121067.08068205</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>84704424.20462848</v>
+        <v>84704424.2046285</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>96692164.63041431</v>
@@ -2321,7 +2321,7 @@
         <v>862.7521669320736</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>944.4276090314042</v>
+        <v>944.4276090314045</v>
       </c>
       <c r="E11" s="156" t="n">
         <v>1026.515586749174</v>
@@ -2333,7 +2333,7 @@
         <v>1173.253128344403</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>90.3362608225179</v>
+        <v>90.33626082251791</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>101.936845945489</v>
@@ -2345,22 +2345,22 @@
         <v>129.0571691126058</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>146.4987473319509</v>
+        <v>146.498747331951</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>5785673.35507804</v>
+        <v>5785673.355078041</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>6615844.72428766</v>
+        <v>6615844.724287662</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>7559820.652161693</v>
+        <v>7559820.652161695</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>8585934.018014137</v>
+        <v>8585934.018014139</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>9892432.734117649</v>
+        <v>9892432.734117651</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2386,31 +2386,31 @@
         <v>103.6543419258557</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>117.0125891016007</v>
+        <v>117.0125891016008</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>132.0971385558854</v>
+        <v>132.0971385558855</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>148.3327710695919</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>168.523171858905</v>
+        <v>168.5231718589051</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>5785673.35507804</v>
+        <v>5785673.355078041</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>6615844.72428766</v>
+        <v>6615844.724287662</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>7559820.652161693</v>
+        <v>7559820.652161695</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>8585934.018014137</v>
+        <v>8585934.018014139</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>9892432.734117649</v>
+        <v>9892432.734117651</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2464,7 +2464,7 @@
         <v>441.3701511308997</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>484.5670739048285</v>
+        <v>484.5670739048284</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>529.9507853868778</v>
@@ -2473,7 +2473,7 @@
         <v>565.7876120372798</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>608.3536715191436</v>
+        <v>608.3536715191437</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>43.77372267350079</v>
@@ -2485,10 +2485,10 @@
         <v>57.11221157929042</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>64.39011985937817</v>
+        <v>64.39011985937816</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>73.60863337916879</v>
+        <v>73.60863337916881</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>68805720.29595971</v>
@@ -2523,7 +2523,7 @@
         <v>672.5810306721954</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>723.1249037892466</v>
+        <v>723.1249037892467</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>51.93641543461127</v>
@@ -2538,7 +2538,7 @@
         <v>76.43903011264504</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>87.39695020932162</v>
+        <v>87.39695020932163</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>68805720.29595971</v>
@@ -2603,16 +2603,16 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>8099.147721008587</v>
+        <v>8099.147721008585</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>8595.59864293624</v>
+        <v>8595.598642936237</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>9254.896493168326</v>
+        <v>9254.89649316832</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>9867.555400585543</v>
+        <v>9867.555400585537</v>
       </c>
       <c r="G13" s="157" t="n">
         <v>10640.47798672073</v>
@@ -2621,31 +2621,31 @@
         <v>7992.866043197648</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>8294.827480241136</v>
+        <v>8294.827480241131</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>8839.763675524764</v>
+        <v>8839.763675524757</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>9439.616233834833</v>
+        <v>9439.616233834828</v>
       </c>
       <c r="L13" s="157" t="n">
         <v>10207.77338497516</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>52982696.5449138</v>
+        <v>52982696.54491379</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>59526547.78476983</v>
+        <v>59526547.7847698</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>69026260.74488486</v>
+        <v>69026260.74488482</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>80046850.86192432</v>
+        <v>80046850.86192429</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>94517953.0863637</v>
+        <v>94517953.08636369</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2656,46 +2656,46 @@
         <v>4547.885147046241</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4826.655438914808</v>
+        <v>4826.655438914805</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>5196.868577856868</v>
+        <v>5196.868577856864</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>5540.892719807121</v>
+        <v>5540.892719807119</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>5974.909146027219</v>
+        <v>5974.909146027218</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>4514.179331211431</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4730.340987965178</v>
+        <v>4730.340987965175</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>5063.346156389451</v>
+        <v>5063.346156389448</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>5403.34278580133</v>
+        <v>5403.342785801327</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>5835.99528125245</v>
+        <v>5835.995281252449</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>52982696.5449138</v>
+        <v>52982696.54491379</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>59526547.78476983</v>
+        <v>59526547.7847698</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>69026260.74488486</v>
+        <v>69026260.74488482</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>80046850.86192432</v>
+        <v>80046850.86192429</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>94517953.0863637</v>
+        <v>94517953.08636369</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2749,13 +2749,13 @@
         <v>749.7765177413177</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>812.1354249803994</v>
+        <v>812.1354249803993</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>888.3690479504158</v>
+        <v>888.3690479504157</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>954.3699197702565</v>
+        <v>954.3699197702564</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>1033.311278604459</v>
@@ -2767,7 +2767,7 @@
         <v>86.94233652242713</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>99.35968543859741</v>
+        <v>99.3596854385974</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>112.7634775504062</v>
@@ -2785,7 +2785,7 @@
         <v>161290505.601675</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>185324949.5103528</v>
+        <v>185324949.5103527</v>
       </c>
       <c r="Q14" s="172" t="n">
         <v>216686391.505133</v>
@@ -2799,7 +2799,7 @@
         <v>852.1761661140486</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>923.5384975904614</v>
+        <v>923.5384975904612</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>1009.742356545031</v>
@@ -2835,7 +2835,7 @@
         <v>161290505.601675</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>185324949.5103528</v>
+        <v>185324949.5103527</v>
       </c>
       <c r="AH14" s="172" t="n">
         <v>216686391.505133</v>
@@ -3205,7 +3205,7 @@
         <v>107324.8202311329</v>
       </c>
       <c r="U19" s="75" t="n">
-        <v>113866.3226073308</v>
+        <v>113866.3226073309</v>
       </c>
       <c r="V19" s="75" t="n">
         <v>120734.9965518909</v>
@@ -3298,7 +3298,7 @@
         <v>20306.62168062228</v>
       </c>
       <c r="F20" s="80" t="n">
-        <v>21723.57111632304</v>
+        <v>21723.57111632305</v>
       </c>
       <c r="G20" s="81" t="n">
         <v>23512.25033249179</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="T20" s="79" t="n">
-        <v>18752.19271124915</v>
+        <v>18752.19271124916</v>
       </c>
       <c r="U20" s="80" t="n">
         <v>19175.16868453016</v>
@@ -3372,7 +3372,7 @@
         <v>269259.0252951058</v>
       </c>
       <c r="AE20" s="80" t="n">
-        <v>271213.3067126184</v>
+        <v>271213.3067126185</v>
       </c>
       <c r="AF20" s="80" t="n">
         <v>273070.8382980569</v>
@@ -3418,7 +3418,7 @@
         <v>166735.1019557571</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>178217.9488561752</v>
+        <v>178217.9488561753</v>
       </c>
       <c r="G21" s="87" t="n">
         <v>192386.4894164148</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>6706.066442755812</v>
+        <v>6706.066442755813</v>
       </c>
       <c r="D22" s="80" t="n">
         <v>7005.136932700228</v>
@@ -3575,7 +3575,7 @@
         <v>7364.545409488179</v>
       </c>
       <c r="F22" s="80" t="n">
-        <v>7855.581932780321</v>
+        <v>7855.581932780322</v>
       </c>
       <c r="G22" s="81" t="n">
         <v>8431.626982386171</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>5187.624522840792</v>
+        <v>5187.624522840793</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>5418.977048339496</v>
@@ -3706,7 +3706,7 @@
         <v>155891.1949973563</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>164552.8887516415</v>
+        <v>164552.8887516416</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>174099.6473652452</v>
@@ -3730,7 +3730,7 @@
         <v>1448930.393389873</v>
       </c>
       <c r="L23" s="87" t="n">
-        <v>1458884.459377357</v>
+        <v>1458884.459377356</v>
       </c>
       <c r="M23" s="85" t="n">
         <v>1571849.870050291</v>
@@ -3742,7 +3742,7 @@
         <v>1615490.66837829</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>1635003.924178828</v>
+        <v>1635003.924178829</v>
       </c>
       <c r="Q23" s="87" t="n">
         <v>1659702.575776157</v>
@@ -3969,7 +3969,7 @@
         <v>1449298.151598933</v>
       </c>
       <c r="L25" s="93" t="n">
-        <v>1459261.001584627</v>
+        <v>1459261.001584626</v>
       </c>
       <c r="M25" s="91" t="n">
         <v>1578478.618268836</v>
@@ -3995,7 +3995,7 @@
         <v>142914.601092674</v>
       </c>
       <c r="U25" s="92" t="n">
-        <v>150793.3453267859</v>
+        <v>150793.345326786</v>
       </c>
       <c r="V25" s="92" t="n">
         <v>159734.3169336306</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>370.9978892145275</v>
+        <v>370.9978892145276</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>418.3876078943426</v>
@@ -4417,7 +4417,7 @@
         <v>461.8198365449502</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>501.5255256500423</v>
+        <v>501.5255256500422</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>543.2039160010985</v>
@@ -4426,22 +4426,22 @@
         <v>39.02551586090195</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>45.95230405395671</v>
+        <v>45.95230405395672</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>53.01581442880892</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>60.72038991108379</v>
+        <v>60.72038991108378</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>69.81479618330782</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>48290754.33143298</v>
+        <v>48290754.33143299</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>57778530.06332128</v>
+        <v>57778530.06332129</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>67623576.82618822</v>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>449.9495478066941</v>
+        <v>449.9495478066942</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>507.4242211419362</v>
+        <v>507.4242211419361</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>560.0992152853061</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>608.254629042549</v>
+        <v>608.2546290425489</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>658.8025524592364</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>48.30375475204972</v>
+        <v>48.30375475204973</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>56.87130733964052</v>
@@ -4488,10 +4488,10 @@
         <v>86.36681440034317</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>48290754.33143298</v>
+        <v>48290754.33143299</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>57778530.06332128</v>
+        <v>57778530.06332129</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>67623576.82618822</v>
@@ -4510,13 +4510,13 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>867.9511022620007</v>
+        <v>867.9511022620004</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>985.93780968825</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1087.877721456031</v>
+        <v>1087.877721456032</v>
       </c>
       <c r="F36" s="156" t="n">
         <v>1161.181346736331</v>
@@ -4525,16 +4525,16 @@
         <v>1233.226475627556</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>61.05638798055656</v>
+        <v>61.05638798055655</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>70.40877805072545</v>
+        <v>70.40877805072546</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>80.55757800454427</v>
+        <v>80.5575780045443</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>91.42927303666254</v>
+        <v>91.42927303666252</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>104.2168409402694</v>
@@ -4543,13 +4543,13 @@
         <v>16508976.50047516</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>19176155.71587477</v>
+        <v>19176155.71587478</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>22091121.32438502</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>25225005.56477446</v>
+        <v>25225005.56477445</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>28995929.61161168</v>
@@ -4560,31 +4560,31 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>880.375791497262</v>
+        <v>880.3757914972616</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>1000.051474454324</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1103.450652442384</v>
+        <v>1103.450652442385</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1177.803616517868</v>
+        <v>1177.803616517867</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>1250.880068873116</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>61.3126207464409</v>
+        <v>61.31262074644089</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>70.70506955690823</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>80.89886661670023</v>
+        <v>80.89886661670025</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>91.8212395347625</v>
+        <v>91.82123953476248</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>104.6701093899318</v>
@@ -4593,13 +4593,13 @@
         <v>16508976.50047516</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>19176155.71587477</v>
+        <v>19176155.71587478</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>22091121.32438502</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>25225005.56477446</v>
+        <v>25225005.56477445</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>28995929.61161168</v>
@@ -4618,7 +4618,7 @@
         <v>488.4530873384645</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>538.0672521757231</v>
+        <v>538.0672521757232</v>
       </c>
       <c r="F37" s="162" t="n">
         <v>581.9331402233031</v>
@@ -4642,13 +4642,13 @@
         <v>75.82642393955732</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>64799730.83190814</v>
+        <v>64799730.83190815</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>76954685.77919605</v>
+        <v>76954685.77919607</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>89714698.15057324</v>
+        <v>89714698.15057325</v>
       </c>
       <c r="P37" s="165" t="n">
         <v>103710930.6220301</v>
@@ -4662,16 +4662,16 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>513.969432806296</v>
+        <v>513.9694328062961</v>
       </c>
       <c r="U37" s="162" t="n">
         <v>578.4262114919924</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>637.3818171240811</v>
+        <v>637.3818171240812</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>689.330671768388</v>
+        <v>689.3306717683879</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>743.3018864955759</v>
@@ -4680,10 +4680,10 @@
         <v>51.06402464502995</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>59.78616200487102</v>
+        <v>59.78616200487103</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>68.80869477334167</v>
+        <v>68.80869477334168</v>
       </c>
       <c r="AB37" s="162" t="n">
         <v>78.60467231983898</v>
@@ -4692,13 +4692,13 @@
         <v>90.1530913608112</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>64799730.83190814</v>
+        <v>64799730.83190815</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>76954685.77919605</v>
+        <v>76954685.77919607</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>89714698.15057324</v>
+        <v>89714698.15057325</v>
       </c>
       <c r="AG37" s="165" t="n">
         <v>103710930.6220301</v>
@@ -4717,7 +4717,7 @@
         <v>887.1898354573774</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>994.033275500011</v>
+        <v>994.0332755000112</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>1087.344229818679</v>
@@ -4729,13 +4729,13 @@
         <v>1261.732447373229</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>92.89505775448769</v>
+        <v>92.89505775448771</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>107.2910362852014</v>
+        <v>107.2910362852015</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>121.8341901660681</v>
+        <v>121.8341901660682</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>138.4396300808439</v>
@@ -4744,19 +4744,19 @@
         <v>157.5467548670326</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>5949553.983914769</v>
+        <v>5949553.98391477</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>6963339.210538107</v>
+        <v>6963339.210538109</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>8007795.956244613</v>
+        <v>8007795.956244615</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>9210131.738712607</v>
+        <v>9210131.738712609</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>10638457.34782425</v>
+        <v>10638457.34782426</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4773,16 +4773,16 @@
         <v>1405.614962919126</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1515.607679291053</v>
+        <v>1515.607679291054</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1631.047426006133</v>
+        <v>1631.047426006134</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>106.5903767992309</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>123.1586265660869</v>
+        <v>123.158626566087</v>
       </c>
       <c r="AA38" s="156" t="n">
         <v>139.9248713204366</v>
@@ -4794,19 +4794,19 @@
         <v>181.2321219792381</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>5949553.983914769</v>
+        <v>5949553.98391477</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>6963339.210538107</v>
+        <v>6963339.210538109</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>8007795.956244613</v>
+        <v>8007795.956244615</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>9210131.738712607</v>
+        <v>9210131.738712609</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>10638457.34782425</v>
+        <v>10638457.34782426</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4828,28 +4828,28 @@
         <v>606.8625767563774</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>654.1617723405408</v>
+        <v>654.1617723405409</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>45.01020495905203</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>52.62589319344213</v>
+        <v>52.62589319344215</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>60.49090596414065</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>69.06470418256437</v>
+        <v>69.06470418256436</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>79.15125086800253</v>
+        <v>79.15125086800255</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>70749284.81582291</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>83918024.98973416</v>
+        <v>83918024.98973417</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>97722494.10681786</v>
@@ -4878,7 +4878,7 @@
         <v>721.408968078104</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>777.5751028264665</v>
+        <v>777.5751028264666</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>53.40347041046789</v>
@@ -4893,13 +4893,13 @@
         <v>81.98833942631744</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>93.977806862449</v>
+        <v>93.97780686244901</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>70749284.81582291</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>83918024.98973416</v>
+        <v>83918024.98973417</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>97722494.10681786</v>
@@ -4918,31 +4918,31 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>8330.742358577028</v>
+        <v>8330.742358577027</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>9048.951092679483</v>
+        <v>9048.951092679479</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>9805.993317618486</v>
+        <v>9805.993317618479</v>
       </c>
       <c r="F40" s="156" t="n">
         <v>10587.50579461968</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>11445.0661360877</v>
+        <v>11445.06613608769</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>8221.421562639012</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>8732.316538836863</v>
+        <v>8732.316538836858</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>9366.140787799071</v>
+        <v>9366.140787799064</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>10128.34359853523</v>
+        <v>10128.34359853522</v>
       </c>
       <c r="L40" s="157" t="n">
         <v>10979.64223402728</v>
@@ -4951,13 +4951,13 @@
         <v>54497733.53724933</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>73136533.95304605</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639945</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>101665002.7819336</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4677.931646828062</v>
+        <v>4677.931646828061</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>5081.224801468374</v>
+        <v>5081.224801468371</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>5506.323985862331</v>
+        <v>5506.323985862327</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>5945.163862453994</v>
+        <v>5945.16386245399</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>6426.706621520081</v>
+        <v>6426.70662152008</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>4643.262015234964</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4979.830495805009</v>
+        <v>4979.830495805007</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>5364.850769643411</v>
+        <v>5364.850769643408</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>5797.578096353359</v>
+        <v>5797.578096353356</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>6277.288675112885</v>
+        <v>6277.288675112884</v>
       </c>
       <c r="AD40" s="158" t="n">
         <v>54497733.53724933</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>73136533.95304605</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639945</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>101665002.7819336</v>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>771.0690040494321</v>
+        <v>771.069004049432</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>854.8270851273844</v>
+        <v>854.8270851273842</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>941.0713391036601</v>
+        <v>941.0713391036597</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>1023.804975493908</v>
@@ -5035,10 +5035,10 @@
         <v>1111.261061845541</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>79.34666767322724</v>
+        <v>79.34666767322723</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>91.51264902085046</v>
+        <v>91.51264902085043</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>105.2541761155981</v>
@@ -5050,7 +5050,7 @@
         <v>139.6272292537644</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>125247018.3530723</v>
+        <v>125247018.3530722</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>146584145.4074306</v>
@@ -5070,13 +5070,13 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>876.3766430825004</v>
+        <v>876.3766430825003</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>972.0863018839888</v>
+        <v>972.0863018839883</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1069.645091548209</v>
+        <v>1069.645091548208</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>1162.790883237964</v>
@@ -5085,22 +5085,22 @@
         <v>1261.242330490019</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>93.70962321175566</v>
+        <v>93.70962321175564</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>108.077360409919</v>
+        <v>108.0773604099189</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>124.289157894237</v>
+        <v>124.2891578942369</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>142.8121327000835</v>
+        <v>142.8121327000834</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>164.7976346686092</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>125247018.3530723</v>
+        <v>125247018.3530722</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>146584145.4074306</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>0.1434249938221721</v>
+        <v>0.1434249938221722</v>
       </c>
       <c r="D46" s="149" t="n">
         <v>0.1607685708913184</v>
@@ -5383,10 +5383,10 @@
         <v>0.2021858754288924</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2244677080283468</v>
+        <v>0.2244677080283469</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.01508697093427497</v>
+        <v>0.01508697093427498</v>
       </c>
       <c r="I46" s="149" t="n">
         <v>0.01765751688750687</v>
@@ -5398,7 +5398,7 @@
         <v>0.0244789239284358</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.02884951088184274</v>
+        <v>0.02884951088184275</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>18668.84244629443</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>0.1739471112654978</v>
+        <v>0.1739471112654979</v>
       </c>
       <c r="U46" s="149" t="n">
         <v>0.1949815561679605</v>
@@ -5433,10 +5433,10 @@
         <v>0.2452128323822507</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2722364376206935</v>
+        <v>0.2722364376206936</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.01867386831113314</v>
+        <v>0.01867386831113315</v>
       </c>
       <c r="Z46" s="149" t="n">
         <v>0.02185322565295459</v>
@@ -5448,7 +5448,7 @@
         <v>0.03028768612392857</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.03568928777405104</v>
+        <v>0.03568928777405105</v>
       </c>
       <c r="AD46" s="151" t="n">
         <v>18668.84244629443</v>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="C47" s="155" t="n">
-        <v>0.03667068873606097</v>
+        <v>0.03667068873606096</v>
       </c>
       <c r="D47" s="156" t="n">
         <v>0.03761897768591695</v>
@@ -5482,10 +5482,10 @@
         <v>0.03783989355901188</v>
       </c>
       <c r="F47" s="156" t="n">
-        <v>0.0371107992466316</v>
+        <v>0.03711079924663159</v>
       </c>
       <c r="G47" s="157" t="n">
-        <v>0.03590058040291845</v>
+        <v>0.03590058040291844</v>
       </c>
       <c r="H47" s="155" t="n">
         <v>0.002579615134018578</v>
@@ -5500,7 +5500,7 @@
         <v>0.00292203574098534</v>
       </c>
       <c r="L47" s="157" t="n">
-        <v>0.003033866975334261</v>
+        <v>0.00303386697533426</v>
       </c>
       <c r="M47" s="158" t="n">
         <v>697.4995907282392</v>
@@ -5515,7 +5515,7 @@
         <v>806.1790866177892</v>
       </c>
       <c r="Q47" s="160" t="n">
-        <v>844.1034335151676</v>
+        <v>844.1034335151675</v>
       </c>
       <c r="S47" s="32" t="inlineStr">
         <is>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="T47" s="155" t="n">
-        <v>0.03719562834429597</v>
+        <v>0.03719562834429596</v>
       </c>
       <c r="U47" s="156" t="n">
-        <v>0.03815749201682525</v>
+        <v>0.03815749201682524</v>
       </c>
       <c r="V47" s="156" t="n">
         <v>0.03838157029280576</v>
@@ -5535,13 +5535,13 @@
         <v>0.03764203902121094</v>
       </c>
       <c r="X47" s="157" t="n">
-        <v>0.03641449593768682</v>
+        <v>0.0364144959376868</v>
       </c>
       <c r="Y47" s="155" t="n">
         <v>0.0025904408959506</v>
       </c>
       <c r="Z47" s="156" t="n">
-        <v>0.002697789259936763</v>
+        <v>0.002697789259936762</v>
       </c>
       <c r="AA47" s="156" t="n">
         <v>0.002813923331129049</v>
@@ -5550,7 +5550,7 @@
         <v>0.002934562802381285</v>
       </c>
       <c r="AC47" s="157" t="n">
-        <v>0.003047062118921275</v>
+        <v>0.003047062118921274</v>
       </c>
       <c r="AD47" s="158" t="n">
         <v>697.4995907282392</v>
@@ -5565,7 +5565,7 @@
         <v>806.1790866177892</v>
       </c>
       <c r="AH47" s="160" t="n">
-        <v>844.1034335151676</v>
+        <v>844.1034335151675</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" thickTop="1">
@@ -5578,16 +5578,16 @@
         <v>0.1298141592574004</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1455654483058414</v>
+        <v>0.1455654483058413</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1634668946710713</v>
       </c>
       <c r="F48" s="162" t="n">
-        <v>0.1820643322285958</v>
+        <v>0.1820643322285957</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.2014222357467069</v>
+        <v>0.201422235746707</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.01284407211229676</v>
@@ -5599,10 +5599,10 @@
         <v>0.01758698434193309</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.02068704679641598</v>
+        <v>0.02068704679641597</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.02433832433609491</v>
+        <v>0.02433832433609492</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>19366.34203702267</v>
@@ -5628,19 +5628,19 @@
         <v>0.1536072404084732</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.1723786233934422</v>
+        <v>0.1723786233934421</v>
       </c>
       <c r="V48" s="162" t="n">
         <v>0.1936390403686031</v>
       </c>
       <c r="W48" s="162" t="n">
-        <v>0.2156648586675134</v>
+        <v>0.2156648586675133</v>
       </c>
       <c r="X48" s="163" t="n">
         <v>0.2385807143902895</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>0.0152612264644724</v>
+        <v>0.01526122646447241</v>
       </c>
       <c r="Z48" s="162" t="n">
         <v>0.0178170630922725</v>
@@ -5652,7 +5652,7 @@
         <v>0.02459235638387516</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.02893681468072447</v>
+        <v>0.02893681468072448</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>19366.34203702267</v>
@@ -5689,7 +5689,7 @@
         <v>0.2321847532512753</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.2416735270707882</v>
+        <v>0.2416735270707883</v>
       </c>
       <c r="H49" s="155" t="n">
         <v>0.02110910401596682</v>
@@ -5698,13 +5698,13 @@
         <v>0.02287827782156765</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.02497553761722078</v>
+        <v>0.02497553761722079</v>
       </c>
       <c r="K49" s="156" t="n">
         <v>0.02741616141002824</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.03017666701568929</v>
+        <v>0.0301766670156893</v>
       </c>
       <c r="M49" s="158" t="n">
         <v>1351.953020224044</v>
@@ -5716,7 +5716,7 @@
         <v>1641.56718950242</v>
       </c>
       <c r="P49" s="159" t="n">
-        <v>1823.946352707775</v>
+        <v>1823.946352707776</v>
       </c>
       <c r="Q49" s="160" t="n">
         <v>2037.701031778493</v>
@@ -5733,7 +5733,7 @@
         <v>0.2740060359181392</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.2881456291855613</v>
+        <v>0.2881456291855614</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.3001463146460073</v>
@@ -5748,7 +5748,7 @@
         <v>0.02626181433471974</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.02868405726245509</v>
+        <v>0.0286840572624551</v>
       </c>
       <c r="AB49" s="156" t="n">
         <v>0.03151095922840506</v>
@@ -5766,7 +5766,7 @@
         <v>1641.56718950242</v>
       </c>
       <c r="AG49" s="159" t="n">
-        <v>1823.946352707775</v>
+        <v>1823.946352707776</v>
       </c>
       <c r="AH49" s="160" t="n">
         <v>2037.701031778493</v>
@@ -5803,13 +5803,13 @@
         <v>0.01788759112293913</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.02096085379095944</v>
+        <v>0.02096085379095943</v>
       </c>
       <c r="L50" s="163" t="n">
         <v>0.02457585982742612</v>
       </c>
       <c r="M50" s="164" t="n">
-        <v>20718.29505724671</v>
+        <v>20718.29505724672</v>
       </c>
       <c r="N50" s="165" t="n">
         <v>24418.34154284851</v>
@@ -5844,7 +5844,7 @@
         <v>0.241431140036283</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>0.01563872850340909</v>
+        <v>0.0156387285034091</v>
       </c>
       <c r="Z50" s="162" t="n">
         <v>0.0181723961452624</v>
@@ -5859,7 +5859,7 @@
         <v>0.02917939240394415</v>
       </c>
       <c r="AD50" s="164" t="n">
-        <v>20718.29505724671</v>
+        <v>20718.29505724672</v>
       </c>
       <c r="AE50" s="165" t="n">
         <v>24418.34154284851</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="C52" s="179" t="n">
-        <v>0.1275498239036652</v>
+        <v>0.1275498239036653</v>
       </c>
       <c r="D52" s="180" t="n">
         <v>0.142399163747896</v>
@@ -6013,7 +6013,7 @@
         <v>0.02443951283443001</v>
       </c>
       <c r="M52" s="182" t="n">
-        <v>20718.29505724671</v>
+        <v>20718.29505724672</v>
       </c>
       <c r="N52" s="183" t="n">
         <v>24418.34154284851</v>
@@ -6063,7 +6063,7 @@
         <v>0.0288451896459773</v>
       </c>
       <c r="AD52" s="188" t="n">
-        <v>20718.29505724671</v>
+        <v>20718.29505724672</v>
       </c>
       <c r="AE52" s="189" t="n">
         <v>24418.34154284851</v>
@@ -6337,13 +6337,13 @@
         <v>0.008182027449917726</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.00763394075610065</v>
+        <v>0.007633940756100649</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007123300657313043</v>
+        <v>0.007123300657313042</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002614860757246542</v>
+        <v>0.0002614860757246541</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>0.000838450183837227</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008177379053139987</v>
+        <v>0.0008177379053139985</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>3.165848129811704e-05</v>
@@ -6370,7 +6370,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="P57" s="152" t="n">
         <v>40.92110070816562</v>
@@ -6387,10 +6387,10 @@
         <v>0.009923235841117234</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009258511412188589</v>
+        <v>0.009258511412188586</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008639202547580492</v>
+        <v>0.00863920254758049</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0003171326440135659</v>
@@ -6420,7 +6420,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="AG57" s="152" t="n">
         <v>40.92110070816562</v>
@@ -6541,7 +6541,7 @@
         <v>0.007138844957788519</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.00669151184420249</v>
+        <v>0.006691511844202488</v>
       </c>
       <c r="E59" s="162" t="n">
         <v>0.006255755851998042</v>
@@ -6559,7 +6559,7 @@
         <v>0.0006891700716674661</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006730407428209137</v>
+        <v>0.0006730407428209135</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>2.608972433166894e-05</v>
@@ -6574,7 +6574,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="P59" s="165" t="n">
         <v>40.92110070816562</v>
@@ -6591,10 +6591,10 @@
         <v>0.008447293268644917</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.007924089222746214</v>
+        <v>0.007924089222746213</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007410421311291649</v>
+        <v>0.007410421311291647</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002719883976691434</v>
@@ -6609,7 +6609,7 @@
         <v>0.0008190342564009413</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0007999936685537255</v>
+        <v>0.0007999936685537253</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>3.101495370681041e-05</v>
@@ -6624,7 +6624,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="AG59" s="165" t="n">
         <v>40.92110070816562</v>
@@ -6745,10 +6745,10 @@
         <v>0.006831748918064954</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006406649286571114</v>
+        <v>0.006406649286571113</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005991132696581429</v>
+        <v>0.005991132696581428</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002199189779151248</v>
@@ -6763,10 +6763,10 @@
         <v>0.0006611205960327989</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006456577621957343</v>
+        <v>0.0006456577621957342</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.50281360815192e-05</v>
+        <v>2.502813608151919e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="P61" s="165" t="n">
         <v>40.92110070816562</v>
@@ -6795,10 +6795,10 @@
         <v>0.008113453275191536</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007613961298568243</v>
+        <v>0.007613961298568241</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007122154855301091</v>
+        <v>0.00712215485530109</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002614290763594598</v>
@@ -6810,10 +6810,10 @@
         <v>0.0008038979279510625</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0007845714363041923</v>
+        <v>0.0007845714363041922</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.000766355816223219</v>
+        <v>0.0007663558162232189</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>2.971149070349159e-05</v>
@@ -6828,7 +6828,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="AG61" s="165" t="n">
         <v>40.92110070816562</v>
@@ -6949,10 +6949,10 @@
         <v>0.006556609709307716</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006147913326186707</v>
+        <v>0.006147913326186706</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.00574501868695714</v>
+        <v>0.005745018686957139</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0002107318399543444</v>
@@ -6967,7 +6967,7 @@
         <v>0.0006581586430969184</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006425519336720359</v>
+        <v>0.0006425519336720358</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>2.489899839840707e-05</v>
@@ -6982,7 +6982,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="P63" s="183" t="n">
         <v>40.92110070816562</v>
@@ -6999,10 +6999,10 @@
         <v>0.007452069240066164</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006991241191972237</v>
+        <v>0.006991241191972235</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006529931137005487</v>
+        <v>0.006529931137005486</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.000239339589250054</v>
@@ -7017,7 +7017,7 @@
         <v>0.0007772919879161402</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007587560103240008</v>
+        <v>0.0007587560103240006</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>2.939530888407141e-05</v>
@@ -7032,7 +7032,7 @@
         <v>1054.23264732392</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1043.054089793218</v>
+        <v>1043.054089793217</v>
       </c>
       <c r="AG63" s="189" t="n">
         <v>40.92110070816562</v>
@@ -7300,10 +7300,10 @@
         <v>0.003472795405995924</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005116953584883514</v>
+        <v>0.005116953584883512</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.006822884135009859</v>
+        <v>0.006822884135009856</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.008413407190420013</v>
@@ -7315,10 +7315,10 @@
         <v>0.0003653056692190322</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005620047117216028</v>
+        <v>0.0005620047117216027</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007832508059357467</v>
+        <v>0.0007832508059357465</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.001018622859566063</v>
@@ -7330,10 +7330,10 @@
         <v>452.0346736994624</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>999.0645549828212</v>
+        <v>999.0645549828208</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1316.650922936778</v>
@@ -7350,10 +7350,10 @@
         <v>0.004211837231368925</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.00620588692981713</v>
+        <v>0.006205886929817128</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008274854710857855</v>
+        <v>0.008274854710857852</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.01020385525334907</v>
@@ -7365,13 +7365,13 @@
         <v>0.0004521563665777949</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0006955460307086227</v>
+        <v>0.0006955460307086226</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009692531459871188</v>
+        <v>0.0009692531459871184</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.001260338466649539</v>
+        <v>0.00126033846664954</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>0.001580448352649789</v>
@@ -7380,10 +7380,10 @@
         <v>452.0346736994624</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>999.0645549828212</v>
+        <v>999.0645549828208</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1316.650922936778</v>
@@ -7504,13 +7504,13 @@
         <v>0.003030025030504441</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004485252979219084</v>
+        <v>0.004485252979219082</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.00599192697436873</v>
+        <v>0.005991926974368728</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007387869355399979</v>
+        <v>0.00738786935539998</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.008725395758803512</v>
@@ -7519,13 +7519,13 @@
         <v>0.0002997967264625996</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004619437563744665</v>
+        <v>0.0004619437563744664</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006446560698927771</v>
+        <v>0.0006446560698927769</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008394461298936524</v>
+        <v>0.0008394461298936525</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.001054310171621748</v>
@@ -7534,10 +7534,10 @@
         <v>452.0346736994624</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>999.0645549828212</v>
+        <v>999.0645549828208</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1316.650922936778</v>
@@ -7554,13 +7554,13 @@
         <v>0.003585385338293547</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005311437179135146</v>
+        <v>0.005311437179135144</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007097895825391496</v>
+        <v>0.007097895825391493</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008751323122344876</v>
+        <v>0.008751323122344877</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01033506129924575</v>
@@ -7569,13 +7569,13 @@
         <v>0.0003562161358057867</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005489904111561256</v>
+        <v>0.0005489904111561255</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007662549107315714</v>
+        <v>0.0007662549107315711</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.0009979171311676068</v>
+        <v>0.0009979171311676072</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.00125351185360678</v>
@@ -7584,10 +7584,10 @@
         <v>452.0346736994624</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>706.6415232151752</v>
+        <v>706.6415232151751</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>999.0645549828212</v>
+        <v>999.0645549828208</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1316.650922936778</v>
@@ -7603,22 +7603,22 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.01125329875724856</v>
+        <v>0.01125329875724857</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.01685371520028444</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.0227071792109998</v>
+        <v>0.02270717921099981</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>0.02819359390889913</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03353583984218843</v>
+        <v>0.03353583984218844</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001178300061839845</v>
+        <v>0.001178300061839846</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.001819106677474751</v>
@@ -7630,10 +7630,10 @@
         <v>0.003329073552468165</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.00418746680397801</v>
+        <v>0.004187466803978011</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.46536916629029</v>
+        <v>75.4653691662903</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>118.0625828027237</v>
@@ -7645,7 +7645,7 @@
         <v>221.4770869308933</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>282.7616920903772</v>
+        <v>282.7616920903773</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         <v>0.02935367659052172</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.0364459904876881</v>
+        <v>0.03644599048768811</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04335193674968969</v>
+        <v>0.04335193674968971</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.001352014311740914</v>
@@ -7674,16 +7674,16 @@
         <v>0.002088139771336047</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.002922072920439438</v>
+        <v>0.002922072920439439</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003826294258021655</v>
+        <v>0.003826294258021656</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004817004928112024</v>
+        <v>0.004817004928112025</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.46536916629029</v>
+        <v>75.4653691662903</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>118.0625828027237</v>
@@ -7695,7 +7695,7 @@
         <v>221.4770869308933</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>282.7616920903772</v>
+        <v>282.7616920903773</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7708,13 +7708,13 @@
         <v>0.003383770602789325</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005011787470122259</v>
+        <v>0.005011787470122256</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.00669899465653046</v>
+        <v>0.006698994656530458</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008266237563967197</v>
+        <v>0.008266237563967199</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.00976709664480834</v>
@@ -7723,10 +7723,10 @@
         <v>0.0003355918735730629</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005171807869024614</v>
+        <v>0.0005171807869024613</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007219432648127878</v>
+        <v>0.0007219432648127876</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.0009407488184716054</v>
@@ -7738,13 +7738,13 @@
         <v>527.5000428657527</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>824.704106017899</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1538.128009867671</v>
+        <v>1538.128009867672</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>1961.409950895459</v>
@@ -7758,13 +7758,13 @@
         <v>0.004018599777152534</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.005956242354977324</v>
+        <v>0.005956242354977321</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007963648901629032</v>
+        <v>0.00796364890162903</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009826504614576017</v>
+        <v>0.00982650461457602</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.0116097447130391</v>
@@ -7773,10 +7773,10 @@
         <v>0.0003981712748621529</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006137537920371582</v>
+        <v>0.0006137537920371579</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008569019879679453</v>
+        <v>0.0008569019879679452</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001116785112694784</v>
@@ -7788,13 +7788,13 @@
         <v>527.5000428657527</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>824.704106017899</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1538.128009867671</v>
+        <v>1538.128009867672</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>1961.409950895459</v>
@@ -7912,13 +7912,13 @@
         <v>0.003247493936677428</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004809383750748596</v>
+        <v>0.004809383750748593</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006423801880995516</v>
+        <v>0.006423801880995514</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007920914638057356</v>
+        <v>0.007920914638057358</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.00935336552586084</v>
@@ -7927,13 +7927,13 @@
         <v>0.000334182570964615</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.000514863713195578</v>
+        <v>0.0005148637131955777</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007184704776558238</v>
+        <v>0.0007184704776558237</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009358948364406543</v>
+        <v>0.0009358948364406544</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.001175227457717899</v>
@@ -7942,13 +7942,13 @@
         <v>527.5000428657527</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>824.704106017899</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1538.128009867671</v>
+        <v>1538.128009867672</v>
       </c>
       <c r="Q74" s="184" t="n">
         <v>1961.409950895459</v>
@@ -7962,13 +7962,13 @@
         <v>0.003691015745295973</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005469101466186546</v>
+        <v>0.005469101466186543</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.00730145299890823</v>
+        <v>0.007301452998908229</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008996212705057363</v>
+        <v>0.008996212705057367</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.01061574182593058</v>
@@ -7977,10 +7977,10 @@
         <v>0.0003946747069202554</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006080592321215541</v>
+        <v>0.000608059232121554</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008484042527836485</v>
+        <v>0.0008484042527836483</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.001104900581139061</v>
@@ -7992,13 +7992,13 @@
         <v>527.5000428657527</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>824.704106017899</v>
+        <v>824.7041060178988</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1166.292607403615</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1538.128009867671</v>
+        <v>1538.128009867672</v>
       </c>
       <c r="AH74" s="190" t="n">
         <v>1961.409950895459</v>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>371.1529690312055</v>
+        <v>371.1529690312056</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>418.5611273595749</v>
@@ -8269,7 +8269,7 @@
         <v>462.0146715083235</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>501.7363864187373</v>
+        <v>501.7363864187372</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>543.4383239360549</v>
@@ -8278,19 +8278,19 @@
         <v>39.04182881043999</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>45.97136202573977</v>
+        <v>45.97136202573978</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>53.0381810173464</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>60.74591911635309</v>
+        <v>60.74591911635308</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>69.84492325294164</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>48310940.21805574</v>
+        <v>48310940.21805575</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>57802492.77026892</v>
@@ -8319,7 +8319,7 @@
         <v>560.3355128660077</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>608.5103628628286</v>
+        <v>608.5103628628285</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>659.0868444927012</v>
@@ -8328,7 +8328,7 @@
         <v>48.32394607294287</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>56.89489379069794</v>
+        <v>56.89489379069795</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>65.63341322972663</v>
@@ -8340,7 +8340,7 @@
         <v>86.40408413646986</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>48310940.21805574</v>
+        <v>48310940.21805575</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>57802492.77026892</v>
@@ -8362,16 +8362,16 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>867.9877729507368</v>
+        <v>867.9877729507365</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>985.975428665936</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1087.91556134959</v>
+        <v>1087.915561349591</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1161.218457535578</v>
+        <v>1161.218457535577</v>
       </c>
       <c r="G80" s="157" t="n">
         <v>1233.262376207959</v>
@@ -8380,13 +8380,13 @@
         <v>61.05896759569058</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>70.41146453482652</v>
+        <v>70.41146453482654</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>80.56038005675744</v>
+        <v>80.56038005675747</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>91.43219507240353</v>
+        <v>91.43219507240352</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>104.2198748072447</v>
@@ -8395,13 +8395,13 @@
         <v>16509674.00006589</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>19176887.39222077</v>
+        <v>19176887.39222078</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>22091889.72478795</v>
+        <v>22091889.72478796</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>25225811.74386108</v>
+        <v>25225811.74386107</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>28996773.7150452</v>
@@ -8412,31 +8412,31 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>880.4129871256063</v>
+        <v>880.4129871256059</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>1000.089631946341</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1103.489034012677</v>
+        <v>1103.489034012678</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1177.841258556889</v>
+        <v>1177.841258556888</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1250.916483369054</v>
+        <v>1250.916483369053</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>61.31521118733686</v>
+        <v>61.31521118733684</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>70.70776734616815</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>80.90168054003135</v>
+        <v>80.90168054003138</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>91.82417409756488</v>
+        <v>91.82417409756486</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>104.6731564520507</v>
@@ -8445,13 +8445,13 @@
         <v>16509674.00006589</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>19176887.39222077</v>
+        <v>19176887.39222078</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>22091889.72478795</v>
+        <v>22091889.72478796</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>25225811.74386108</v>
+        <v>25225811.74386107</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>28996773.7150452</v>
@@ -8470,10 +8470,10 @@
         <v>488.6098295515936</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>538.2429667532206</v>
+        <v>538.2429667532207</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>582.1228220375664</v>
+        <v>582.1228220375662</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>627.7442221911277</v>
@@ -8482,13 +8482,13 @@
         <v>42.99008257673623</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>50.32274904231797</v>
+        <v>50.32274904231798</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>57.90818163819755</v>
+        <v>57.90818163819756</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>66.14366423859838</v>
+        <v>66.14366423859835</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>75.85181657406503</v>
@@ -8497,10 +8497,10 @@
         <v>64820614.21812163</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>76979380.16248968</v>
+        <v>76979380.1624897</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>89743995.9385674</v>
+        <v>89743995.93856741</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>103744735.3259034</v>
@@ -8520,10 +8520,10 @@
         <v>578.6118256417876</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>637.5899644815864</v>
+        <v>637.5899644815865</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>689.5553599385756</v>
+        <v>689.5553599385754</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>743.5508022712654</v>
@@ -8535,10 +8535,10 @@
         <v>59.80534709263085</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>68.83116536727088</v>
+        <v>68.8311653672709</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>78.63029360830774</v>
+        <v>78.63029360830772</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>90.18328168734554</v>
@@ -8547,10 +8547,10 @@
         <v>64820614.21812163</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>76979380.16248968</v>
+        <v>76979380.1624897</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>89743995.9385674</v>
+        <v>89743995.93856741</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>103744735.3259034</v>
@@ -8569,10 +8569,10 @@
         <v>887.402690251104</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>994.262092583524</v>
+        <v>994.2620925835242</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1087.589838358154</v>
+        <v>1087.589838358155</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>1172.691882152108</v>
@@ -8581,31 +8581,31 @@
         <v>1262.007656740142</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>92.9173451585655</v>
+        <v>92.91734515856551</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>107.3157336697005</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>121.8617099860885</v>
+        <v>121.8617099860886</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>138.4703753158064</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>157.5811190008522</v>
+        <v>157.5811190008523</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>5950981.402304159</v>
+        <v>5950981.40230416</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>6964942.105540656</v>
+        <v>6964942.105540658</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>8009604.751486536</v>
+        <v>8009604.751486538</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>9212177.162152246</v>
+        <v>9212177.162152248</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>10640777.81054812</v>
@@ -8628,7 +8628,7 @@
         <v>1515.944271596187</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1631.40319043975</v>
+        <v>1631.403190439751</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>106.615949987471</v>
@@ -8637,25 +8637,25 @@
         <v>123.186976520193</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>139.9564774506194</v>
+        <v>139.9564774506195</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>159.1519062665829</v>
+        <v>159.151906266583</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>181.2716523706915</v>
+        <v>181.2716523706916</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>5950981.402304159</v>
+        <v>5950981.40230416</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>6964942.105540656</v>
+        <v>6964942.105540658</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>8009604.751486536</v>
+        <v>8009604.751486538</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>9212177.162152246</v>
+        <v>9212177.162152248</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>10640777.81054812</v>
@@ -8680,28 +8680,28 @@
         <v>607.0552432101225</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>654.3746516791932</v>
+        <v>654.3746516791931</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>45.0243989384059</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>52.64238449860646</v>
+        <v>52.64238449860647</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>60.51016115629061</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>69.0866308133099</v>
+        <v>69.08663081330988</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>79.17700851183123</v>
+        <v>79.17700851183122</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>70771595.62042579</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>83944322.26803035</v>
+        <v>83944322.26803036</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>97753600.69005394</v>
@@ -8721,7 +8721,7 @@
         <v>539.152028962682</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>606.2692353587687</v>
+        <v>606.2692353587686</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>667.4785982727459</v>
@@ -8730,7 +8730,7 @@
         <v>721.6380006678584</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>777.8281437112158</v>
+        <v>777.8281437112157</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>53.42031120817411</v>
@@ -8745,13 +8745,13 @@
         <v>82.01436904687857</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>94.00838940979246</v>
+        <v>94.00838940979244</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>70771595.62042579</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>83944322.26803035</v>
+        <v>83944322.26803036</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>97753600.69005394</v>
@@ -8770,31 +8770,31 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>8330.742358577028</v>
+        <v>8330.742358577027</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>9048.951092679483</v>
+        <v>9048.951092679479</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>9805.993317618486</v>
+        <v>9805.993317618479</v>
       </c>
       <c r="F84" s="156" t="n">
         <v>10587.50579461968</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>11445.0661360877</v>
+        <v>11445.06613608769</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>8221.421562639012</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>8732.316538836863</v>
+        <v>8732.316538836858</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>9366.140787799071</v>
+        <v>9366.140787799064</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>10128.34359853523</v>
+        <v>10128.34359853522</v>
       </c>
       <c r="L84" s="157" t="n">
         <v>10979.64223402728</v>
@@ -8803,13 +8803,13 @@
         <v>54497733.53724933</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>73136533.95304605</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639945</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>101665002.7819336</v>
@@ -8820,46 +8820,46 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4677.931646828062</v>
+        <v>4677.931646828061</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>5081.224801468374</v>
+        <v>5081.224801468371</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>5506.323985862331</v>
+        <v>5506.323985862327</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>5945.163862453994</v>
+        <v>5945.16386245399</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>6426.706621520081</v>
+        <v>6426.70662152008</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>4643.262015234964</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4979.830495805009</v>
+        <v>4979.830495805007</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>5364.850769643411</v>
+        <v>5364.850769643408</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>5797.578096353359</v>
+        <v>5797.578096353356</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>6277.288675112885</v>
+        <v>6277.288675112884</v>
       </c>
       <c r="AD84" s="158" t="n">
         <v>54497733.53724933</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>62666120.41769642</v>
+        <v>62666120.41769639</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>73136533.95304605</v>
+        <v>73136533.95304601</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>85887179.0363995</v>
+        <v>85887179.03639945</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>101665002.7819336</v>
@@ -8875,10 +8875,10 @@
         <v>771.2063579769816</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>854.9804415882091</v>
+        <v>854.980441588209</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>941.2426704887986</v>
+        <v>941.2426704887984</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>1023.989593286697</v>
@@ -8896,7 +8896,7 @@
         <v>105.2733386838713</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>120.9893827565632</v>
+        <v>120.9893827565631</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>139.6528439940565</v>
@@ -8925,7 +8925,7 @@
         <v>876.5327559249412</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>972.2606947143831</v>
+        <v>972.2606947143829</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>1069.839831062129</v>
@@ -9334,7 +9334,7 @@
         <v>107324.8202311329</v>
       </c>
       <c r="U90" s="75" t="n">
-        <v>113866.3226073308</v>
+        <v>113866.3226073309</v>
       </c>
       <c r="V90" s="75" t="n">
         <v>120734.9965518909</v>
@@ -9413,7 +9413,7 @@
         <v>20306.62168062228</v>
       </c>
       <c r="F91" s="80" t="n">
-        <v>21723.57111632304</v>
+        <v>21723.57111632305</v>
       </c>
       <c r="G91" s="81" t="n">
         <v>23512.25033249179</v>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="T91" s="79" t="n">
-        <v>18752.19271124915</v>
+        <v>18752.19271124916</v>
       </c>
       <c r="U91" s="80" t="n">
         <v>19175.16868453016</v>
@@ -9487,7 +9487,7 @@
         <v>269259.0252951058</v>
       </c>
       <c r="AE91" s="80" t="n">
-        <v>271213.3067126184</v>
+        <v>271213.3067126185</v>
       </c>
       <c r="AF91" s="80" t="n">
         <v>273070.8382980569</v>
@@ -9533,7 +9533,7 @@
         <v>166735.1019557571</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>178217.9488561752</v>
+        <v>178217.9488561753</v>
       </c>
       <c r="G92" s="87" t="n">
         <v>192386.4894164148</v>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>6706.066442755812</v>
+        <v>6706.066442755813</v>
       </c>
       <c r="D93" s="80" t="n">
         <v>7005.136932700228</v>
@@ -9645,7 +9645,7 @@
         <v>7364.545409488179</v>
       </c>
       <c r="F93" s="80" t="n">
-        <v>7855.581932780321</v>
+        <v>7855.581932780322</v>
       </c>
       <c r="G93" s="81" t="n">
         <v>8431.626982386171</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>5187.624522840792</v>
+        <v>5187.624522840793</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>5418.977048339496</v>
@@ -9759,7 +9759,7 @@
         <v>155891.1949973563</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>164552.8887516415</v>
+        <v>164552.8887516416</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>174099.6473652452</v>
@@ -9783,7 +9783,7 @@
         <v>1448930.393389873</v>
       </c>
       <c r="L94" s="87" t="n">
-        <v>1458884.459377357</v>
+        <v>1458884.459377356</v>
       </c>
       <c r="M94" s="85" t="n">
         <v>1571849.870050291</v>
@@ -9795,7 +9795,7 @@
         <v>1615490.66837829</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>1635003.924178828</v>
+        <v>1635003.924178829</v>
       </c>
       <c r="Q94" s="87" t="n">
         <v>1659702.575776157</v>
@@ -10015,7 +10015,7 @@
         <v>1449298.151598933</v>
       </c>
       <c r="L96" s="134" t="n">
-        <v>1459261.001584627</v>
+        <v>1459261.001584626</v>
       </c>
       <c r="M96" s="132" t="n">
         <v>1578478.618268836</v>
@@ -10041,7 +10041,7 @@
         <v>142914.601092674</v>
       </c>
       <c r="U96" s="136" t="n">
-        <v>150793.3453267859</v>
+        <v>150793.345326786</v>
       </c>
       <c r="V96" s="136" t="n">
         <v>159734.3169336306</v>
